--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8416918442634798</v>
+        <v>0.8391540031874755</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8453298412063625</v>
+        <v>0.8337853789914142</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8419430459193876</v>
+        <v>0.8274246883819935</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8372271486683319</v>
+        <v>0.8224467342946442</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8391540031874755</v>
+        <v>0.8400670257509418</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8337853789914142</v>
+        <v>0.8348779218304363</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8274246883819935</v>
+        <v>0.8276032380888587</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8224467342946442</v>
+        <v>0.8262959114278485</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8400670257509418</v>
+        <v>0.8418291976037814</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8348779218304363</v>
+        <v>0.8327714310872041</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8276032380888587</v>
+        <v>0.8269066012482021</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8262959114278485</v>
+        <v>0.8135793022418166</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8418291976037814</v>
+        <v>0.8393653025565531</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8327714310872041</v>
+        <v>0.836587358885196</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8269066012482021</v>
+        <v>0.8311404989383833</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8135793022418166</v>
+        <v>0.8258164652152228</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8393653025565531</v>
+        <v>0.8375663760320837</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.836587358885196</v>
+        <v>0.8374639015300185</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8311404989383833</v>
+        <v>0.8284457119535965</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8258164652152228</v>
+        <v>0.8256629086318024</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8375663760320837</v>
+        <v>0.842528554246547</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8374639015300185</v>
+        <v>0.8331078590718223</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8284457119535965</v>
+        <v>0.8299060904582195</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8256629086318024</v>
+        <v>0.8219693320728817</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.842528554246547</v>
+        <v>0.8437862521620554</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8331078590718223</v>
+        <v>0.8359409451666636</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8299060904582195</v>
+        <v>0.8322731868927462</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8219693320728817</v>
+        <v>0.822693054424249</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8437862521620554</v>
+        <v>0.8401628145515341</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8359409451666636</v>
+        <v>0.8297161757349139</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8322731868927462</v>
+        <v>0.8272108055971483</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.822693054424249</v>
+        <v>0.8218948669883618</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8401628145515341</v>
+        <v>0.8366581664678689</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8297161757349139</v>
+        <v>0.8319549957522533</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8272108055971483</v>
+        <v>0.82562614198634</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8218948669883618</v>
+        <v>0.8186308458113718</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8366581664678689</v>
+        <v>0.839727365388262</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8319549957522533</v>
+        <v>0.8329931845887062</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.82562614198634</v>
+        <v>0.8340420621688711</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8186308458113718</v>
+        <v>0.8294316623482555</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.839727365388262</v>
+        <v>0.8441441653167899</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8329931845887062</v>
+        <v>0.8389993123024851</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8340420621688711</v>
+        <v>0.8365176261003509</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8294316623482555</v>
+        <v>0.8332032687572806</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8441441653167899</v>
+        <v>0.8416918442634798</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8389993123024851</v>
+        <v>0.8453298412063625</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8365176261003509</v>
+        <v>0.8419430459193876</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8332032687572806</v>
+        <v>0.8372271486683319</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8416918442634798</v>
+        <v>0.8411955801789412</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8453298412063625</v>
+        <v>0.845797373067391</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8419430459193876</v>
+        <v>0.850055656500215</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8372271486683319</v>
+        <v>0.8350085325150862</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8411955801789412</v>
+        <v>0.8441441653167899</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.845797373067391</v>
+        <v>0.8389993123024851</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.850055656500215</v>
+        <v>0.8365176261003509</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8350085325150862</v>
+        <v>0.8332032687572806</v>
       </c>
     </row>
   </sheetData>

--- a/results/MHD/deepwalk_embedding_size_results.xlsx
+++ b/results/MHD/deepwalk_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8441441653167899</v>
+        <v>0.8425166913923517</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8389993123024851</v>
+        <v>0.8425984722024238</v>
       </c>
     </row>
     <row r="4">
@@ -461,15 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8365176261003509</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.8332032687572806</v>
+        <v>0.8442424706663694</v>
       </c>
     </row>
   </sheetData>
